--- a/database/AllData.xlsx
+++ b/database/AllData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EDS\260108AWESIM\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{692F0F95-F172-4591-B9B2-C553E02F2265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9FBD90C-255E-48DE-90DB-6B9D019953F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="8" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wall_New" sheetId="12" r:id="rId1"/>
@@ -30,6 +30,7 @@
     <sheet name="RoofR" sheetId="17" r:id="rId15"/>
     <sheet name="GlazedR" sheetId="20" r:id="rId16"/>
     <sheet name="RoofMid" sheetId="21" r:id="rId17"/>
+    <sheet name="Sheet1" sheetId="22" r:id="rId18"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Roof_New!$A$1:$E$66</definedName>
@@ -54,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="255">
   <si>
     <t>LAYERS</t>
   </si>
@@ -816,6 +817,9 @@
   </si>
   <si>
     <t>GypBoard</t>
+  </si>
+  <si>
+    <t>ECSBC</t>
   </si>
 </sst>
 </file>
@@ -7174,6 +7178,21 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CC89ACC-2300-439D-98CE-11D0F6243F6D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8927A4B8-1031-407E-BF73-BC2490A82C6C}">
   <dimension ref="A1:S66"/>

--- a/database/AllData.xlsx
+++ b/database/AllData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EDS\260108AWESIM\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9FBD90C-255E-48DE-90DB-6B9D019953F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9F948BB-6ECD-4397-AAC8-9414252E789B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="8" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wall_New" sheetId="12" r:id="rId1"/>
@@ -826,10 +826,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.00000"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -932,7 +931,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -956,7 +955,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10211,10 +10209,10 @@
         <v>246</v>
       </c>
       <c r="R1" t="s">
+        <v>249</v>
+      </c>
+      <c r="S1" t="s">
         <v>247</v>
-      </c>
-      <c r="S1" t="s">
-        <v>249</v>
       </c>
       <c r="T1" t="s">
         <v>102</v>
@@ -10280,9 +10278,9 @@
       <c r="R3">
         <v>0.25</v>
       </c>
-      <c r="S3" s="21">
-        <f>R3/0.87</f>
-        <v>0.28735632183908044</v>
+      <c r="S3" s="7">
+        <f>R3*0.87</f>
+        <v>0.2175</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.3">
@@ -10326,9 +10324,9 @@
       <c r="R4">
         <v>0.3</v>
       </c>
-      <c r="S4" s="21">
-        <f t="shared" ref="S4:S10" si="0">R4/0.87</f>
-        <v>0.34482758620689652</v>
+      <c r="S4" s="7">
+        <f t="shared" ref="S4:S9" si="0">R4*0.87</f>
+        <v>0.26100000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
@@ -10372,9 +10370,9 @@
       <c r="R5">
         <v>0.4</v>
       </c>
-      <c r="S5" s="21">
+      <c r="S5" s="7">
         <f t="shared" si="0"/>
-        <v>0.45977011494252878</v>
+        <v>0.34800000000000003</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
@@ -10418,9 +10416,9 @@
       <c r="R6">
         <v>0.5</v>
       </c>
-      <c r="S6" s="21">
+      <c r="S6" s="7">
         <f t="shared" si="0"/>
-        <v>0.57471264367816088</v>
+        <v>0.435</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
@@ -10464,9 +10462,9 @@
       <c r="R7">
         <v>0.6</v>
       </c>
-      <c r="S7" s="21">
+      <c r="S7" s="7">
         <f t="shared" si="0"/>
-        <v>0.68965517241379304</v>
+        <v>0.52200000000000002</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.3">
@@ -10510,9 +10508,9 @@
       <c r="R8">
         <v>0.7</v>
       </c>
-      <c r="S8" s="21">
+      <c r="S8" s="7">
         <f t="shared" si="0"/>
-        <v>0.80459770114942519</v>
+        <v>0.60899999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
@@ -10556,9 +10554,9 @@
       <c r="R9">
         <v>0.8</v>
       </c>
-      <c r="S9" s="21">
+      <c r="S9" s="7">
         <f t="shared" si="0"/>
-        <v>0.91954022988505757</v>
+        <v>0.69600000000000006</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.3">
@@ -10602,9 +10600,9 @@
       <c r="R10">
         <v>0.9</v>
       </c>
-      <c r="S10" s="21">
-        <f t="shared" si="0"/>
-        <v>1.0344827586206897</v>
+      <c r="S10" s="7">
+        <f>R10*0.87</f>
+        <v>0.78300000000000003</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
